--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Bluechip Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Bluechip Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="226">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Bluechip Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -76,6 +76,15 @@
     <t>INE090A01021</t>
   </si>
   <si>
+    <t>Reliance Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
     <t>Larsen &amp; Toubro Ltd.</t>
   </si>
   <si>
@@ -85,6 +94,39 @@
     <t>Construction</t>
   </si>
   <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki India Ltd.</t>
+  </si>
+  <si>
+    <t>INE585B01010</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>Ultratech Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE481G01011</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
     <t>Infosys Ltd.</t>
   </si>
   <si>
@@ -94,48 +136,6 @@
     <t>It - Software</t>
   </si>
   <si>
-    <t>Maruti Suzuki India Ltd.</t>
-  </si>
-  <si>
-    <t>INE585B01010</t>
-  </si>
-  <si>
-    <t>Automobiles</t>
-  </si>
-  <si>
-    <t>Reliance Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE002A01018</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE481G01011</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
     <t>Sun Pharmaceutical Industries Ltd.</t>
   </si>
   <si>
@@ -145,19 +145,43 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>INE733E01010</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
     <t>Hero Motocorp Ltd.</t>
   </si>
   <si>
     <t>INE158A01026</t>
   </si>
   <si>
-    <t>NTPC Ltd.</t>
-  </si>
-  <si>
-    <t>INE733E01010</t>
-  </si>
-  <si>
-    <t>Power</t>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE726G01019</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
   </si>
   <si>
     <t>ITC Ltd.</t>
@@ -169,22 +193,10 @@
     <t>Diversified Fmcg</t>
   </si>
   <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE726G01019</t>
-  </si>
-  <si>
-    <t>Insurance</t>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
   </si>
   <si>
     <t>Oil &amp; Natural Gas Corporation Ltd.</t>
@@ -196,34 +208,130 @@
     <t>Oil</t>
   </si>
   <si>
+    <t>DLF Ltd.</t>
+  </si>
+  <si>
+    <t>INE271C01023</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>Asian Paints Ltd.</t>
+  </si>
+  <si>
+    <t>INE021A01026</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>HDFC Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE795G01014</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>HDFC Asset Management Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE127D01025</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Bharat Petroleum Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE029A01011</t>
+  </si>
+  <si>
+    <t>Coal India Ltd.</t>
+  </si>
+  <si>
+    <t>INE522F01014</t>
+  </si>
+  <si>
+    <t>Consumable Fuels</t>
+  </si>
+  <si>
+    <t>Procter &amp; Gamble Hygiene and Health Care Ltd.</t>
+  </si>
+  <si>
+    <t>INE179A01014</t>
+  </si>
+  <si>
+    <t>Personal Products</t>
+  </si>
+  <si>
+    <t>Tata Motors Ltd.</t>
+  </si>
+  <si>
+    <t>INE155A01022</t>
+  </si>
+  <si>
     <t>Power Grid Corporation Of India Ltd.</t>
   </si>
   <si>
     <t>INE752E01010</t>
   </si>
   <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>Coal India Ltd.</t>
-  </si>
-  <si>
-    <t>INE522F01014</t>
-  </si>
-  <si>
-    <t>Consumable Fuels</t>
-  </si>
-  <si>
-    <t>DLF Ltd.</t>
-  </si>
-  <si>
-    <t>INE271C01023</t>
-  </si>
-  <si>
-    <t>Realty</t>
+    <t>HCL Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE860A01027</t>
+  </si>
+  <si>
+    <t>Zydus Lifesciences Ltd.</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
+  </si>
+  <si>
+    <t>United Spirits Ltd.</t>
+  </si>
+  <si>
+    <t>INE854D01024</t>
+  </si>
+  <si>
+    <t>Beverages</t>
+  </si>
+  <si>
+    <t>United Breweries Ltd.</t>
+  </si>
+  <si>
+    <t>INE686F01025</t>
+  </si>
+  <si>
+    <t>Dr. Reddy's Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE089A01031</t>
+  </si>
+  <si>
+    <t>Avenue Supermarts Ltd.</t>
+  </si>
+  <si>
+    <t>INE192R01011</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
   </si>
   <si>
     <t>Tech Mahindra Ltd.</t>
@@ -232,54 +340,60 @@
     <t>INE669C01036</t>
   </si>
   <si>
-    <t>HDFC Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE795G01014</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE101A01026</t>
-  </si>
-  <si>
-    <t>Tata Motors Ltd.</t>
-  </si>
-  <si>
-    <t>INE155A01022</t>
-  </si>
-  <si>
-    <t>HCL Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE860A01027</t>
-  </si>
-  <si>
-    <t>HDFC Asset Management Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE127D01025</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Procter &amp; Gamble Hygiene and Health Care Ltd.</t>
-  </si>
-  <si>
-    <t>INE179A01014</t>
-  </si>
-  <si>
-    <t>Personal Products</t>
-  </si>
-  <si>
     <t>Shree Cements Ltd.</t>
   </si>
   <si>
     <t>INE070A01015</t>
   </si>
   <si>
+    <t>Union Bank Of India</t>
+  </si>
+  <si>
+    <t>INE692A01016</t>
+  </si>
+  <si>
+    <t>Bank Of Baroda</t>
+  </si>
+  <si>
+    <t>INE028A01039</t>
+  </si>
+  <si>
+    <t>Lupin Ltd.</t>
+  </si>
+  <si>
+    <t>INE326A01037</t>
+  </si>
+  <si>
+    <t>Hindustan Aeronautics Ltd.</t>
+  </si>
+  <si>
+    <t>INE066F01020</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Aurobindo Pharma Ltd.</t>
+  </si>
+  <si>
+    <t>INE406A01037</t>
+  </si>
+  <si>
+    <t>Hyundai Motor India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0V6F01027</t>
+  </si>
+  <si>
+    <t>Siemens Ltd.</t>
+  </si>
+  <si>
+    <t>INE003A01024</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
     <t>Hindalco Industries Ltd.</t>
   </si>
   <si>
@@ -289,118 +403,25 @@
     <t>Non - Ferrous Metals</t>
   </si>
   <si>
-    <t>United Breweries Ltd.</t>
-  </si>
-  <si>
-    <t>INE686F01025</t>
-  </si>
-  <si>
-    <t>Beverages</t>
-  </si>
-  <si>
-    <t>Bharat Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE029A01011</t>
-  </si>
-  <si>
-    <t>Asian Paints Ltd.</t>
-  </si>
-  <si>
-    <t>INE021A01026</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>United Spirits Ltd.</t>
-  </si>
-  <si>
-    <t>INE854D01024</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
-  </si>
-  <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>Siemens Ltd.</t>
-  </si>
-  <si>
-    <t>INE003A01024</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
-  </si>
-  <si>
     <t>Wipro Ltd.</t>
   </si>
   <si>
     <t>INE075A01022</t>
   </si>
   <si>
-    <t>Dr. Reddy's Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE089A01031</t>
-  </si>
-  <si>
-    <t>Hindustan Aeronautics Ltd.</t>
-  </si>
-  <si>
-    <t>INE066F01020</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>Union Bank Of India</t>
-  </si>
-  <si>
-    <t>INE692A01016</t>
-  </si>
-  <si>
-    <t>Bank Of Baroda</t>
-  </si>
-  <si>
-    <t>INE028A01039</t>
-  </si>
-  <si>
-    <t>Tata Consultancy Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE467B01029</t>
-  </si>
-  <si>
-    <t>ICICI Securities Ltd.</t>
-  </si>
-  <si>
-    <t>INE763G01038</t>
-  </si>
-  <si>
-    <t>Aurobindo Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE406A01037</t>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>ABB India Ltd.</t>
+  </si>
+  <si>
+    <t>INE117A01022</t>
   </si>
   <si>
     <t>Bajaj Auto Ltd.</t>
@@ -409,16 +430,25 @@
     <t>INE917I01010</t>
   </si>
   <si>
-    <t>Lupin Ltd.</t>
-  </si>
-  <si>
-    <t>INE326A01037</t>
-  </si>
-  <si>
-    <t>Hindustan Petroleum Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE094A01015</t>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
+  </si>
+  <si>
+    <t>Max Financial Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE180A01020</t>
   </si>
   <si>
     <t>NHPC Ltd.</t>
@@ -427,40 +457,13 @@
     <t>INE848E01016</t>
   </si>
   <si>
-    <t>Hyundai Motor India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0V6F01027</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>Muthoot Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE414G01012</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Grasim Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE047A01021</t>
-  </si>
-  <si>
-    <t>Max Financial Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE180A01020</t>
+    <t>Page Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE761H01022</t>
+  </si>
+  <si>
+    <t>Textiles &amp; Apparels</t>
   </si>
   <si>
     <t>TVS Motor Company Ltd.</t>
@@ -475,91 +478,73 @@
     <t>INE059A01026</t>
   </si>
   <si>
+    <t>Oil India Ltd.</t>
+  </si>
+  <si>
+    <t>INE274J01014</t>
+  </si>
+  <si>
+    <t>Ashok Leyland Ltd.</t>
+  </si>
+  <si>
+    <t>INE208A01029</t>
+  </si>
+  <si>
+    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
+  </si>
+  <si>
+    <t>Life Insurance Corporation of India</t>
+  </si>
+  <si>
+    <t>INE0J1Y01017</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd. - Partly Paid Share</t>
+  </si>
+  <si>
+    <t>IN9397D01014</t>
+  </si>
+  <si>
+    <t>Gillette India Ltd.</t>
+  </si>
+  <si>
+    <t>INE322A01010</t>
+  </si>
+  <si>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>Gujarat Pipavav Port Ltd.</t>
+  </si>
+  <si>
+    <t>INE517F01014</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
     <t>LTIMindtree Ltd.</t>
   </si>
   <si>
     <t>INE214T01019</t>
   </si>
   <si>
-    <t>Ambuja Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE079A01024</t>
-  </si>
-  <si>
-    <t>Life Insurance Corporation of India</t>
-  </si>
-  <si>
-    <t>INE0J1Y01017</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd. - Partly Paid Share</t>
-  </si>
-  <si>
-    <t>IN9397D01014</t>
-  </si>
-  <si>
-    <t>Gillette India Ltd.</t>
-  </si>
-  <si>
-    <t>INE322A01010</t>
-  </si>
-  <si>
-    <t>Tata Steel Ltd.</t>
-  </si>
-  <si>
-    <t>INE081A01020</t>
-  </si>
-  <si>
-    <t>Ferrous Metals</t>
-  </si>
-  <si>
-    <t>ICICI Lombard General Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE765G01017</t>
-  </si>
-  <si>
-    <t>Gujarat Pipavav Port Ltd.</t>
-  </si>
-  <si>
-    <t>INE517F01014</t>
-  </si>
-  <si>
-    <t>Transport Infrastructure</t>
-  </si>
-  <si>
-    <t>GAIL (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE129A01019</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>Ashok Leyland Ltd.</t>
-  </si>
-  <si>
-    <t>INE208A01029</t>
-  </si>
-  <si>
-    <t>Agricultural, Commercial &amp; Construction Vehicles</t>
-  </si>
-  <si>
     <t>Birla Corporation Ltd.</t>
   </si>
   <si>
     <t>INE340A01012</t>
   </si>
   <si>
-    <t>ITC Hotels Ltd</t>
-  </si>
-  <si>
-    <t>INE379A01028</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
+    <t>Swiggy Ltd</t>
+  </si>
+  <si>
+    <t>INE00H001014</t>
   </si>
   <si>
     <t>Syngene International Ltd.</t>
@@ -571,6 +556,15 @@
     <t>Healthcare Services</t>
   </si>
   <si>
+    <t>Indian Oil Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE242A01010</t>
+  </si>
+  <si>
+    <t>^</t>
+  </si>
+  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -604,43 +598,34 @@
     <t>Treasury Bills</t>
   </si>
   <si>
+    <t>182 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Y423</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X409</t>
-  </si>
-  <si>
-    <t>SOV</t>
-  </si>
-  <si>
-    <t>IN002024X342</t>
-  </si>
-  <si>
-    <t>IN002024X417</t>
-  </si>
-  <si>
-    <t>IN002024X425</t>
-  </si>
-  <si>
-    <t>182 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002024Y225</t>
-  </si>
-  <si>
-    <t>364 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002023Z489</t>
-  </si>
-  <si>
-    <t>IN002024X383</t>
-  </si>
-  <si>
-    <t>IN002024Z040</t>
-  </si>
-  <si>
-    <t>^</t>
+    <t>IN002025X042</t>
+  </si>
+  <si>
+    <t>IN002025X026</t>
+  </si>
+  <si>
+    <t>IN002025X034</t>
+  </si>
+  <si>
+    <t>IN002024X490</t>
+  </si>
+  <si>
+    <t>IN002024Y415</t>
+  </si>
+  <si>
+    <t>IN002024X516</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -676,9 +661,6 @@
     <t>Index Futures</t>
   </si>
   <si>
-    <t>Ambuja Cements Ltd. $$</t>
-  </si>
-  <si>
     <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
   </si>
   <si>
@@ -697,7 +679,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -985,10 +967,10 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1085,13 +1067,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>150</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1109,7 +1091,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="27698700"/>
+          <a:off x="666750" y="27127200"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1124,13 +1106,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>158</xdr:row>
+      <xdr:row>155</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>168</xdr:row>
+      <xdr:row>165</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1148,7 +1130,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="30556200"/>
+          <a:off x="666750" y="29984700"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1482,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J157"/>
+  <dimension ref="B1:J154"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
@@ -1582,10 +1564,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>5808973.590000001</v>
+        <v>6367383.530000001</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9177334329304996</v>
+        <v>0.9127223006824995</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1619,10 +1601,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>5808973.590000001</v>
+        <v>6367383.530000001</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9177334329304996</v>
+        <v>0.9127223006824995</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1645,13 +1627,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>34294013</v>
+        <v>34665562</v>
       </c>
       <c r="G8" s="15">
-        <v>582569.55</v>
+        <v>674210.52</v>
       </c>
       <c r="H8" s="16">
-        <v>0.0920375251773</v>
+        <v>0.0966436172819</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1674,13 +1656,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>40518440</v>
+        <v>43364687</v>
       </c>
       <c r="G9" s="15">
-        <v>507615.02</v>
+        <v>626966.64</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0801957983963</v>
+        <v>0.0898715196623</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1703,13 +1685,13 @@
         <v>22</v>
       </c>
       <c r="F10" s="14">
-        <v>11492922</v>
+        <v>31400781</v>
       </c>
       <c r="G10" s="15">
-        <v>409998.50</v>
+        <v>446173.70</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0647738064346</v>
+        <v>0.0639560478885</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1732,13 +1714,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="14">
-        <v>16573722</v>
+        <v>11876248</v>
       </c>
       <c r="G11" s="15">
-        <v>311552.83</v>
+        <v>436463.99</v>
       </c>
       <c r="H11" s="16">
-        <v>0.049220820819</v>
+        <v>0.0625642252021</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1761,13 +1743,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="14">
-        <v>2370209</v>
+        <v>16706913</v>
       </c>
       <c r="G12" s="15">
-        <v>291788.13</v>
+        <v>310113.72</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0460982853658</v>
+        <v>0.0444527499653</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1787,16 +1769,16 @@
         <v>13</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F13" s="14">
-        <v>22854559</v>
+        <v>25197029</v>
       </c>
       <c r="G13" s="15">
-        <v>289133.03</v>
+        <v>300398.98</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0456788181398</v>
+        <v>0.0430602062617</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1807,25 +1789,25 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>34</v>
-      </c>
       <c r="F14" s="14">
-        <v>17522281</v>
+        <v>2358549</v>
       </c>
       <c r="G14" s="15">
-        <v>284964.86</v>
+        <v>290549.65</v>
       </c>
       <c r="H14" s="16">
-        <v>0.045020307836</v>
+        <v>0.041648369972</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1836,25 +1818,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="D15" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>37</v>
-      </c>
       <c r="F15" s="14">
-        <v>2377728</v>
+        <v>2370478</v>
       </c>
       <c r="G15" s="15">
-        <v>273140.32</v>
+        <v>265730.58</v>
       </c>
       <c r="H15" s="16">
-        <v>0.043152202306</v>
+        <v>0.0380907204972</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1865,25 +1847,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="D16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F16" s="14">
-        <v>23807059</v>
+        <v>15429639</v>
       </c>
       <c r="G16" s="15">
-        <v>234761.41</v>
+        <v>241118.97</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0370888921049</v>
+        <v>0.0345628090408</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1906,13 +1888,13 @@
         <v>42</v>
       </c>
       <c r="F17" s="14">
-        <v>10239095</v>
+        <v>11295632</v>
       </c>
       <c r="G17" s="15">
-        <v>178564.70</v>
+        <v>189495.52</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0282106283653</v>
+        <v>0.0271629290381</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1932,16 +1914,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F18" s="14">
-        <v>3129370</v>
+        <v>48034862</v>
       </c>
       <c r="G18" s="15">
-        <v>135788.06</v>
+        <v>160388.40</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0214525407155</v>
+        <v>0.0229906159667</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1952,25 +1934,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F19" s="14">
-        <v>38471089</v>
+        <v>3155899</v>
       </c>
       <c r="G19" s="15">
-        <v>124646.33</v>
+        <v>135997.16</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0196923092455</v>
+        <v>0.0194942930918</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1993,13 +1975,13 @@
         <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>27496058</v>
+        <v>2279989</v>
       </c>
       <c r="G20" s="15">
-        <v>123044.86</v>
+        <v>121523.41</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0194393002521</v>
+        <v>0.0174195767915</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -2022,13 +2004,13 @@
         <v>53</v>
       </c>
       <c r="F21" s="14">
-        <v>2538868</v>
+        <v>16844782</v>
       </c>
       <c r="G21" s="15">
-        <v>109789.54</v>
+        <v>111579.84</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0173451522688</v>
+        <v>0.0159942318214</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -2048,16 +2030,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="F22" s="14">
-        <v>16759926</v>
+        <v>3476669</v>
       </c>
       <c r="G22" s="15">
-        <v>103241.14</v>
+        <v>103493.48</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0163106002057</v>
+        <v>0.014835105617</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -2068,25 +2050,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>59</v>
-      </c>
       <c r="F23" s="14">
-        <v>35459414</v>
+        <v>23207795</v>
       </c>
       <c r="G23" s="15">
-        <v>93119.97</v>
+        <v>97020.19</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0147116023887</v>
+        <v>0.0139072023245</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2097,25 +2079,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>61</v>
-      </c>
       <c r="D24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F24" s="14">
-        <v>25068189</v>
+        <v>5073394</v>
       </c>
       <c r="G24" s="15">
-        <v>75618.19</v>
+        <v>91940.05</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0119465754191</v>
+        <v>0.0131789978671</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2126,25 +2108,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="D25" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>56</v>
-      </c>
       <c r="F25" s="14">
-        <v>5073394</v>
+        <v>36539783</v>
       </c>
       <c r="G25" s="15">
-        <v>75268.87</v>
+        <v>87476.24</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0118913879341</v>
+        <v>0.0125391402374</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2167,13 +2149,13 @@
         <v>66</v>
       </c>
       <c r="F26" s="14">
-        <v>18689446</v>
+        <v>10862303</v>
       </c>
       <c r="G26" s="15">
-        <v>73991.52</v>
+        <v>86664.88</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0116895851918</v>
+        <v>0.0124228371495</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2196,13 +2178,13 @@
         <v>69</v>
       </c>
       <c r="F27" s="14">
-        <v>9924179</v>
+        <v>3747237</v>
       </c>
       <c r="G27" s="15">
-        <v>73940.1</v>
+        <v>84653.83</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0116814615789</v>
+        <v>0.0121345664377</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2222,16 +2204,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="F28" s="14">
-        <v>4105901</v>
+        <v>10634342</v>
       </c>
       <c r="G28" s="15">
-        <v>68751.26</v>
+        <v>82612.89</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0108617002437</v>
+        <v>0.0118420111921</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2251,16 +2233,16 @@
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="F29" s="14">
-        <v>10633497</v>
+        <v>2352901</v>
       </c>
       <c r="G29" s="15">
-        <v>67847.03</v>
+        <v>76895.16</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0107188450406</v>
+        <v>0.0110224124267</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2271,25 +2253,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="F30" s="14">
-        <v>2268328</v>
+        <v>1542480</v>
       </c>
       <c r="G30" s="15">
-        <v>67819.6</v>
+        <v>73776.82</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0107145114991</v>
+        <v>0.0105754190195</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2300,25 +2282,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F31" s="14">
-        <v>9381915</v>
+        <v>19993150</v>
       </c>
       <c r="G31" s="15">
-        <v>67183.89</v>
+        <v>63658.19</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0106140785548</v>
+        <v>0.0091249803566</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2329,25 +2311,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="F32" s="14">
-        <v>3877223</v>
+        <v>15414871</v>
       </c>
       <c r="G32" s="15">
-        <v>66899.54</v>
+        <v>61243.28</v>
       </c>
       <c r="H32" s="16">
-        <v>0.010569155386</v>
+        <v>0.0087788189858</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2358,25 +2340,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F33" s="14">
-        <v>1542480</v>
+        <v>443240</v>
       </c>
       <c r="G33" s="15">
-        <v>59692.43</v>
+        <v>60209.72</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0094305367127</v>
+        <v>0.0086306649981</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2387,25 +2369,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="F34" s="14">
-        <v>397389</v>
+        <v>8357848</v>
       </c>
       <c r="G34" s="15">
-        <v>57623.79</v>
+        <v>60134.72</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0091037216465</v>
+        <v>0.0086199142443</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2416,25 +2398,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F35" s="14">
-        <v>195388</v>
+        <v>20418726</v>
       </c>
       <c r="G35" s="15">
-        <v>54309.85</v>
+        <v>59163.26</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0085801672723</v>
+        <v>0.0084806618807</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2445,25 +2427,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F36" s="14">
-        <v>9064030</v>
+        <v>3256315</v>
       </c>
       <c r="G36" s="15">
-        <v>53867.53</v>
+        <v>53292.85</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0085102871384</v>
+        <v>0.0076391774475</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2474,25 +2456,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F37" s="14">
-        <v>2474641</v>
+        <v>5118449</v>
       </c>
       <c r="G37" s="15">
-        <v>53105.80</v>
+        <v>47601.58</v>
       </c>
       <c r="H37" s="16">
-        <v>0.008389944865</v>
+        <v>0.006823371548</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2512,16 +2494,16 @@
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="F38" s="14">
-        <v>20309699</v>
+        <v>3102769</v>
       </c>
       <c r="G38" s="15">
-        <v>53028.62</v>
+        <v>47165.19</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0083777515463</v>
+        <v>0.0067608179287</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2532,25 +2514,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>98</v>
-      </c>
       <c r="F39" s="14">
-        <v>2206482</v>
+        <v>2339694</v>
       </c>
       <c r="G39" s="15">
-        <v>50766.74</v>
+        <v>46251.07</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0080204073675</v>
+        <v>0.0066297848748</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2570,16 +2552,16 @@
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F40" s="14">
-        <v>3402769</v>
+        <v>3655647</v>
       </c>
       <c r="G40" s="15">
-        <v>48455.43</v>
+        <v>45739.46</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0076552539668</v>
+        <v>0.0065564489663</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2602,13 +2584,13 @@
         <v>103</v>
       </c>
       <c r="F41" s="14">
-        <v>1622121</v>
+        <v>1098117</v>
       </c>
       <c r="G41" s="15">
-        <v>47269.42</v>
+        <v>43947.74</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0074678816175</v>
+        <v>0.0062996177588</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2628,16 +2610,16 @@
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="F42" s="14">
-        <v>1238262</v>
+        <v>1257147</v>
       </c>
       <c r="G42" s="15">
-        <v>45377.97</v>
+        <v>43540.03</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0071690599969</v>
+        <v>0.0062411752278</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2648,25 +2630,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>108</v>
-      </c>
       <c r="D43" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="F43" s="14">
-        <v>657450</v>
+        <v>2765864</v>
       </c>
       <c r="G43" s="15">
-        <v>39929.24</v>
+        <v>43531.93</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0063082398175</v>
+        <v>0.0062400141464</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2677,25 +2659,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F44" s="14">
-        <v>3979988</v>
+        <v>146026</v>
       </c>
       <c r="G44" s="15">
-        <v>38615.83</v>
+        <v>43216.39</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0061007401191</v>
+        <v>0.0061947835751</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2706,25 +2688,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F45" s="14">
-        <v>12211168</v>
+        <v>27796952</v>
       </c>
       <c r="G45" s="15">
-        <v>38086.63</v>
+        <v>40803.15</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0060171342074</v>
+        <v>0.0058488615877</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2735,25 +2717,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="F46" s="14">
-        <v>2988642</v>
+        <v>15307156</v>
       </c>
       <c r="G46" s="15">
-        <v>36382.23</v>
+        <v>38199.01</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0057478637694</v>
+        <v>0.0054755753484</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2764,25 +2746,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="F47" s="14">
-        <v>866924</v>
+        <v>1905863</v>
       </c>
       <c r="G47" s="15">
-        <v>34129.06</v>
+        <v>37311.08</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0053918956441</v>
+        <v>0.0053482964577</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2793,25 +2775,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="F48" s="14">
-        <v>27796952</v>
+        <v>726554</v>
       </c>
       <c r="G48" s="15">
-        <v>32102.70</v>
+        <v>36139.52</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0050717602035</v>
+        <v>0.0051803610831</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2822,25 +2804,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="F49" s="14">
-        <v>14807156</v>
+        <v>3078275</v>
       </c>
       <c r="G49" s="15">
-        <v>31596.99</v>
+        <v>35332.44</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0049918653706</v>
+        <v>0.0050646715049</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2851,25 +2833,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F50" s="14">
-        <v>761356</v>
+        <v>1748537</v>
       </c>
       <c r="G50" s="15">
-        <v>31310</v>
+        <v>32298.98</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0049465251201</v>
+        <v>0.0046298450841</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2880,25 +2862,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="F51" s="14">
-        <v>3352608</v>
+        <v>894319</v>
       </c>
       <c r="G51" s="15">
-        <v>27779.71</v>
+        <v>29204.88</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0043887905891</v>
+        <v>0.0041863263205</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2909,25 +2891,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="D52" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D52" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>42</v>
-      </c>
       <c r="F52" s="14">
-        <v>2334499</v>
+        <v>4448722</v>
       </c>
       <c r="G52" s="15">
-        <v>27357.99</v>
+        <v>28182.65</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0043221649559</v>
+        <v>0.0040397964134</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2947,16 +2929,16 @@
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F53" s="14">
-        <v>289700</v>
+        <v>10805133</v>
       </c>
       <c r="G53" s="15">
-        <v>25632.08</v>
+        <v>26977.18</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0040494962504</v>
+        <v>0.0038670002646</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2976,16 +2958,16 @@
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="F54" s="14">
-        <v>1158021</v>
+        <v>16678971</v>
       </c>
       <c r="G54" s="15">
-        <v>24092.05</v>
+        <v>26856.48</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0038061938844</v>
+        <v>0.0038496987182</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2996,25 +2978,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="F55" s="14">
-        <v>6299733</v>
+        <v>439514</v>
       </c>
       <c r="G55" s="15">
-        <v>22568.79</v>
+        <v>26243.38</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0035655409347</v>
+        <v>0.0037618148896</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -3025,25 +3007,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F56" s="14">
-        <v>27830953</v>
+        <v>289700</v>
       </c>
       <c r="G56" s="15">
-        <v>22417.83</v>
+        <v>24934.48</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0035416914479</v>
+        <v>0.0035741927347</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -3054,25 +3036,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="F57" s="14">
-        <v>1201476</v>
+        <v>893990</v>
       </c>
       <c r="G57" s="15">
-        <v>20155.36</v>
+        <v>22154.41</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0031842540576</v>
+        <v>0.0031756880939</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3083,25 +3065,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F58" s="14">
-        <v>4529314</v>
+        <v>4822192</v>
       </c>
       <c r="G58" s="15">
-        <v>19992.39</v>
+        <v>21003.06</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0031585071653</v>
+        <v>0.003010649689</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3112,25 +3094,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="F59" s="14">
-        <v>700485</v>
+        <v>1218821</v>
       </c>
       <c r="G59" s="15">
-        <v>15822.56</v>
+        <v>18315.22</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0024997346057</v>
+        <v>0.0026253656085</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3150,16 +3132,16 @@
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F60" s="14">
-        <v>621126</v>
+        <v>19873589</v>
       </c>
       <c r="G60" s="15">
-        <v>15583.12</v>
+        <v>17371.50</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0024619065643</v>
+        <v>0.0024900895904</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3179,16 +3161,16 @@
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="F61" s="14">
-        <v>1218821</v>
+        <v>33220</v>
       </c>
       <c r="G61" s="15">
-        <v>13599</v>
+        <v>15407.44</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0021484444301</v>
+        <v>0.0022085545841</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3199,25 +3181,25 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F62" s="14">
-        <v>476097</v>
+        <v>380349</v>
       </c>
       <c r="G62" s="15">
-        <v>11701.99</v>
+        <v>10576.74</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0018487444104</v>
+        <v>0.0015161057004</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3228,10 +3210,10 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
@@ -3240,13 +3222,13 @@
         <v>42</v>
       </c>
       <c r="F63" s="14">
-        <v>589318</v>
+        <v>688832</v>
       </c>
       <c r="G63" s="15">
-        <v>8718.37</v>
+        <v>10096.21</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0013773757972</v>
+        <v>0.0014472249042</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3257,25 +3239,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="F64" s="14">
-        <v>140845</v>
+        <v>2211155</v>
       </c>
       <c r="G64" s="15">
-        <v>8329.78</v>
+        <v>9437.21</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0013159842227</v>
+        <v>0.0013527616143</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3286,25 +3268,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c r="F65" s="14">
-        <v>1465999</v>
+        <v>3917229</v>
       </c>
       <c r="G65" s="15">
-        <v>7517.64</v>
+        <v>9245.84</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0011876779017</v>
+        <v>0.001325329991</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3315,25 +3297,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F66" s="14">
         <v>741417</v>
       </c>
       <c r="G66" s="15">
-        <v>6268.31</v>
+        <v>7076.45</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0009903019123</v>
+        <v>0.0010143622877</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3344,25 +3326,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F67" s="14">
         <v>450000</v>
       </c>
       <c r="G67" s="15">
-        <v>5396.63</v>
+        <v>6308.10</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0008525891363</v>
+        <v>0.0009042243988</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3373,10 +3355,10 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
@@ -3388,10 +3370,10 @@
         <v>59209</v>
       </c>
       <c r="G68" s="15">
-        <v>5096.27</v>
+        <v>5579.26</v>
       </c>
       <c r="H68" s="16">
-        <v>0.00080513662</v>
+        <v>0.000799750007</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3402,25 +3384,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F69" s="14">
-        <v>3358241</v>
+        <v>3141909</v>
       </c>
       <c r="G69" s="15">
-        <v>4520.86</v>
+        <v>4810.89</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0007142301997</v>
+        <v>0.0006896092513</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3431,25 +3413,25 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>56</v>
+        <v>170</v>
       </c>
       <c r="F70" s="14">
-        <v>217807</v>
+        <v>2588163</v>
       </c>
       <c r="G70" s="15">
-        <v>4047.94</v>
+        <v>4041.42</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0006395157104</v>
+        <v>0.0005793108178</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3460,25 +3442,25 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D71" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>170</v>
+        <v>39</v>
       </c>
       <c r="F71" s="14">
-        <v>2588163</v>
+        <v>70845</v>
       </c>
       <c r="G71" s="15">
-        <v>3927.80</v>
+        <v>3591.06</v>
       </c>
       <c r="H71" s="16">
-        <v>0.0006205353358</v>
+        <v>0.0005147546915</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>13</v>
@@ -3489,25 +3471,25 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>173</v>
+        <v>36</v>
       </c>
       <c r="F72" s="14">
-        <v>1965646</v>
+        <v>199999</v>
       </c>
       <c r="G72" s="15">
-        <v>3481.55</v>
+        <v>2748.79</v>
       </c>
       <c r="H72" s="16">
-        <v>0.0005500343191</v>
+        <v>0.0003940208597</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>13</v>
@@ -3518,25 +3500,25 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D73" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>176</v>
+        <v>103</v>
       </c>
       <c r="F73" s="14">
-        <v>1367524</v>
+        <v>669747</v>
       </c>
       <c r="G73" s="15">
-        <v>2965.20</v>
+        <v>2230.59</v>
       </c>
       <c r="H73" s="16">
-        <v>0.0004684585207</v>
+        <v>0.0003197403183</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>13</v>
@@ -3556,16 +3538,16 @@
         <v>13</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="F74" s="14">
-        <v>199999</v>
+        <v>101175</v>
       </c>
       <c r="G74" s="15">
-        <v>2334.99</v>
+        <v>654.15</v>
       </c>
       <c r="H74" s="16">
-        <v>0.0003688944966</v>
+        <v>0.0000937680744</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>13</v>
@@ -3576,25 +3558,25 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D75" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F75" s="14">
-        <v>1205438</v>
+        <v>219713</v>
       </c>
       <c r="G75" s="15">
-        <v>1964.26</v>
-      </c>
-      <c r="H75" s="16">
-        <v>0.0003103245427</v>
+        <v>311.93</v>
+      </c>
+      <c r="H75" s="17" t="s">
+        <v>182</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>13</v>
@@ -3605,35 +3587,35 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="C76" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="15" customHeight="1">
+      <c r="B77" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D76" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="13" t="s">
+      <c r="C77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F76" s="14">
-        <v>135621</v>
-      </c>
-      <c r="G76" s="15">
-        <v>1012.61</v>
-      </c>
-      <c r="H76" s="16">
-        <v>0.0001599776685</v>
-      </c>
-      <c r="I76" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" ht="15" customHeight="1">
-      <c r="B77" s="12" t="s">
+      <c r="H77" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I77" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J77" s="11" t="s">
@@ -3641,399 +3623,399 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="15" customHeight="1">
+      <c r="B79" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="9" t="s">
+      <c r="C79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1">
+      <c r="B80" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1">
+      <c r="B81" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15" customHeight="1">
+      <c r="B82" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="15" customHeight="1">
+      <c r="B83" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="H78" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I78" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" ht="15" customHeight="1">
-      <c r="B79" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="7" t="s">
+      <c r="C83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1">
+      <c r="B84" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" ht="15" customHeight="1">
+      <c r="B85" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H80" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H82" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I82" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="7" t="s">
+      <c r="C85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1">
+      <c r="B86" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1">
+      <c r="B87" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C84" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H84" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I84" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="7" t="s">
+      <c r="C87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" ht="15" customHeight="1">
+      <c r="B88" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" ht="15" customHeight="1">
+      <c r="B89" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C86" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I86" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="7" t="s">
+      <c r="C89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" ht="15" customHeight="1">
+      <c r="B90" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J90" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" ht="15" customHeight="1">
+      <c r="B91" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="C88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I88" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J88" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="7" t="s">
+      <c r="C91" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="9">
+        <v>59574.70</v>
+      </c>
+      <c r="H91" s="10">
+        <v>0.0085396390823</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J91" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" ht="15" customHeight="1">
+      <c r="B92" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J92" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" ht="15" customHeight="1">
+      <c r="B93" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C90" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H90" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I90" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J90" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J91" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="7" t="s">
+      <c r="C93" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" ht="15" customHeight="1">
+      <c r="B94" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J94" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" ht="15" customHeight="1">
+      <c r="B95" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C92" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G92" s="9">
-        <v>53699.99</v>
-      </c>
-      <c r="H92" s="10">
-        <v>0.008483818252000001</v>
-      </c>
-      <c r="I92" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J92" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J93" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10" ht="15" customHeight="1">
-      <c r="B94" s="7" t="s">
+      <c r="C95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J95" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" ht="15" customHeight="1">
+      <c r="B96" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" ht="15" customHeight="1">
+      <c r="B97" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C94" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I94" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J94" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J95" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="96" spans="2:10" ht="15" customHeight="1">
-      <c r="B96" s="7" t="s">
+      <c r="C97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="9">
+        <v>59574.70</v>
+      </c>
+      <c r="H97" s="10">
+        <v>0.0085396390823</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J97" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" ht="15" customHeight="1">
+      <c r="B98" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="C96" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F96" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H96" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="I96" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J96" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J97" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98" spans="2:10" ht="15" customHeight="1">
-      <c r="B98" s="7" t="s">
+      <c r="C98" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G98" s="9">
-        <v>53699.99</v>
-      </c>
-      <c r="H98" s="10">
-        <v>0.008483818252000001</v>
-      </c>
-      <c r="I98" s="9" t="s">
-        <v>13</v>
+      <c r="D98" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="F98" s="14">
+        <v>15000000</v>
+      </c>
+      <c r="G98" s="15">
+        <v>14862.87</v>
+      </c>
+      <c r="H98" s="16">
+        <v>0.0021304940777</v>
+      </c>
+      <c r="I98" s="15">
+        <v>5.61</v>
       </c>
       <c r="J98" s="11" t="s">
         <v>13</v>
@@ -4041,28 +4023,28 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
       <c r="B99" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="D99" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C99" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D99" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>198</v>
-      </c>
       <c r="F99" s="14">
-        <v>21600000</v>
+        <v>14500000</v>
       </c>
       <c r="G99" s="15">
-        <v>21340.71</v>
+        <v>14382.78</v>
       </c>
       <c r="H99" s="16">
-        <v>0.0033715221365</v>
+        <v>0.0020616763526</v>
       </c>
       <c r="I99" s="15">
-        <v>6.52</v>
+        <v>5.61</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>13</v>
@@ -4070,7 +4052,7 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
       <c r="B100" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C100" s="13" t="s">
         <v>199</v>
@@ -4079,19 +4061,19 @@
         <v>13</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F100" s="14">
-        <v>15000000</v>
+        <v>10000000</v>
       </c>
       <c r="G100" s="15">
-        <v>14931.66</v>
+        <v>9939</v>
       </c>
       <c r="H100" s="16">
-        <v>0.0023589853489</v>
+        <v>0.0014246898908</v>
       </c>
       <c r="I100" s="15">
-        <v>6.43</v>
+        <v>5.60</v>
       </c>
       <c r="J100" s="11" t="s">
         <v>13</v>
@@ -4099,7 +4081,7 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C101" s="13" t="s">
         <v>200</v>
@@ -4108,19 +4090,19 @@
         <v>13</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F101" s="14">
-        <v>10350000</v>
+        <v>10000000</v>
       </c>
       <c r="G101" s="15">
-        <v>10213.22</v>
+        <v>9929.77</v>
       </c>
       <c r="H101" s="16">
-        <v>0.0016135403796</v>
+        <v>0.0014233668314</v>
       </c>
       <c r="I101" s="15">
-        <v>6.52</v>
+        <v>5.61</v>
       </c>
       <c r="J101" s="11" t="s">
         <v>13</v>
@@ -4128,7 +4110,7 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
       <c r="B102" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C102" s="13" t="s">
         <v>201</v>
@@ -4137,19 +4119,19 @@
         <v>13</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F102" s="14">
-        <v>5000000</v>
+        <v>6300000</v>
       </c>
       <c r="G102" s="15">
-        <v>4927.89</v>
+        <v>6289.20</v>
       </c>
       <c r="H102" s="16">
-        <v>0.0007785350263</v>
+        <v>0.0009015152089</v>
       </c>
       <c r="I102" s="15">
-        <v>6.51</v>
+        <v>5.70</v>
       </c>
       <c r="J102" s="11" t="s">
         <v>13</v>
@@ -4157,28 +4139,28 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
       <c r="B103" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C103" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C103" s="13" t="s">
-        <v>203</v>
-      </c>
       <c r="D103" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F103" s="14">
-        <v>1000000</v>
+        <v>3000000</v>
       </c>
       <c r="G103" s="15">
-        <v>995.44</v>
+        <v>2975.75</v>
       </c>
       <c r="H103" s="16">
-        <v>0.0001572650579</v>
+        <v>0.0004265540741</v>
       </c>
       <c r="I103" s="15">
-        <v>6.43</v>
+        <v>5.61</v>
       </c>
       <c r="J103" s="11" t="s">
         <v>13</v>
@@ -4186,28 +4168,28 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
       <c r="B104" s="12" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D104" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F104" s="14">
-        <v>600000</v>
+        <v>1200000</v>
       </c>
       <c r="G104" s="15">
-        <v>598.74</v>
+        <v>1195.33</v>
       </c>
       <c r="H104" s="16">
-        <v>0.0000945922213</v>
+        <v>0.0001713426468</v>
       </c>
       <c r="I104" s="15">
-        <v>6.42</v>
+        <v>5.70</v>
       </c>
       <c r="J104" s="11" t="s">
         <v>13</v>
@@ -4215,57 +4197,36 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
       <c r="B105" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C105" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="F105" s="14">
-        <v>500000</v>
-      </c>
-      <c r="G105" s="15">
-        <v>495.21</v>
-      </c>
-      <c r="H105" s="16">
-        <v>0.0000782359854</v>
-      </c>
-      <c r="I105" s="15">
-        <v>6.43</v>
+        <v>13</v>
       </c>
       <c r="J105" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C106" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="F106" s="14">
-        <v>200000</v>
-      </c>
-      <c r="G106" s="15">
-        <v>197.12</v>
-      </c>
-      <c r="H106" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="I106" s="15">
-        <v>6.51</v>
+      <c r="C106" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H106" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J106" s="11" t="s">
         <v>13</v>
@@ -4281,7 +4242,7 @@
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1">
       <c r="B108" s="7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>13</v>
@@ -4296,10 +4257,10 @@
         <v>13</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I108" s="9" t="s">
         <v>13</v>
@@ -4318,7 +4279,7 @@
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
       <c r="B110" s="7" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>13</v>
@@ -4332,11 +4293,11 @@
       <c r="F110" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G110" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="H110" s="10" t="s">
-        <v>186</v>
+      <c r="G110" s="9">
+        <v>542489.16</v>
+      </c>
+      <c r="H110" s="10">
+        <v>0.0777622318302</v>
       </c>
       <c r="I110" s="9" t="s">
         <v>13</v>
@@ -4355,7 +4316,7 @@
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
       <c r="B112" s="7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>13</v>
@@ -4370,10 +4331,10 @@
         <v>13</v>
       </c>
       <c r="G112" s="9">
-        <v>447531.16000000003</v>
+        <v>7135.4418668</v>
       </c>
       <c r="H112" s="10">
-        <v>0.07070342143029999</v>
+        <v>0.0010228183815</v>
       </c>
       <c r="I112" s="9" t="s">
         <v>13</v>
@@ -4384,6 +4345,20 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
       <c r="B113" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C113" s="13"/>
+      <c r="D113" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" s="13"/>
+      <c r="G113" s="15">
+        <v>7135.4418668</v>
+      </c>
+      <c r="H113" s="16">
+        <v>0.0010228183815</v>
+      </c>
+      <c r="I113" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J113" s="11" t="s">
@@ -4391,260 +4366,216 @@
       </c>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J114" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="2:10" ht="15" customHeight="1">
+      <c r="B115" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" s="19">
+        <v>-327.8140831710771</v>
+      </c>
+      <c r="H115" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="I115" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J115" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="116" spans="2:10" ht="15" customHeight="1">
+      <c r="B116" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" s="19">
+        <v>6976255.01778363</v>
+      </c>
+      <c r="H116" s="21">
+        <v>0.9999999999965844</v>
+      </c>
+      <c r="I116" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J116" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="2:8" ht="15" customHeight="1">
+      <c r="B118" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H118" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8" ht="15" customHeight="1">
+      <c r="B119" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E119" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F119" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G119" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H119" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8" ht="15" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="C114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="9">
-        <v>12135.4418668</v>
-      </c>
-      <c r="H114" s="10">
-        <v>0.001917223508</v>
-      </c>
-      <c r="I114" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J114" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="115" spans="2:10" ht="15" customHeight="1">
-      <c r="B115" s="12" t="s">
+      <c r="C120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="2:10" ht="15" customHeight="1">
+      <c r="B121" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="C115" s="13"/>
-      <c r="D115" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="13"/>
-      <c r="G115" s="15">
-        <v>12135.4418668</v>
-      </c>
-      <c r="H115" s="16">
-        <v>0.001917223508</v>
-      </c>
-      <c r="I115" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J115" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="116" spans="2:10" ht="15" customHeight="1">
-      <c r="B116" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J116" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="117" spans="2:10" ht="15" customHeight="1">
-      <c r="B117" s="18" t="s">
+      <c r="C121" s="13"/>
+      <c r="D121" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="C117" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D117" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E117" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F117" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="19">
-        <v>7355.764185611159</v>
-      </c>
-      <c r="H117" s="20">
-        <v>0.001162103874862847</v>
-      </c>
-      <c r="I117" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J117" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="118" spans="2:10" ht="15" customHeight="1">
-      <c r="B118" s="18" t="s">
+      <c r="F121" s="14">
+        <v>398175</v>
+      </c>
+      <c r="G121" s="15">
+        <v>99030.90</v>
+      </c>
+      <c r="H121" s="16">
+        <v>0.0141954242996</v>
+      </c>
+      <c r="I121" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J121" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="2:9" ht="15" customHeight="1">
+      <c r="B125" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="C118" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D118" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F118" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="19">
-        <v>6329695.94605241</v>
-      </c>
-      <c r="H118" s="20">
-        <v>0.9999999999956625</v>
-      </c>
-      <c r="I118" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J118" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="120" spans="2:8" ht="15" customHeight="1">
-      <c r="B120" s="19" t="s">
+      <c r="C125" s="22"/>
+      <c r="D125" s="22"/>
+      <c r="E125" s="22"/>
+      <c r="F125" s="22"/>
+      <c r="G125" s="22"/>
+      <c r="H125" s="22"/>
+      <c r="I125" s="22"/>
+    </row>
+    <row r="129" spans="2:9" ht="15" customHeight="1">
+      <c r="B129" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="C120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H120" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="121" spans="2:8" ht="15" customHeight="1">
-      <c r="B121" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C121" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D121" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E121" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F121" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G121" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H121" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="122" spans="2:8" ht="15" customHeight="1">
-      <c r="B122" s="7" t="s">
+      <c r="C129" s="22"/>
+      <c r="D129" s="22"/>
+      <c r="E129" s="22"/>
+      <c r="F129" s="22"/>
+      <c r="G129" s="22"/>
+      <c r="H129" s="22"/>
+      <c r="I129" s="22"/>
+    </row>
+    <row r="130" spans="2:8" ht="15" customHeight="1">
+      <c r="B130" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="C122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G122" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H122" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="123" spans="2:10" ht="15" customHeight="1">
-      <c r="B123" s="12" t="s">
+      <c r="C130" s="22"/>
+      <c r="D130" s="22"/>
+      <c r="E130" s="22"/>
+      <c r="F130" s="22"/>
+      <c r="G130" s="22"/>
+      <c r="H130" s="22"/>
+    </row>
+    <row r="131" spans="2:8" ht="15" customHeight="1">
+      <c r="B131" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="C123" s="13"/>
-      <c r="D123" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" s="13" t="s">
+      <c r="C131" s="22"/>
+      <c r="D131" s="22"/>
+      <c r="E131" s="22"/>
+      <c r="F131" s="22"/>
+      <c r="G131" s="22"/>
+      <c r="H131" s="22"/>
+    </row>
+    <row r="132" spans="2:8" ht="15" customHeight="1">
+      <c r="B132" s="13" t="s">
         <v>219</v>
-      </c>
-      <c r="F123" s="14">
-        <v>713700</v>
-      </c>
-      <c r="G123" s="15">
-        <v>168577.37</v>
-      </c>
-      <c r="H123" s="16">
-        <v>0.0266327753239</v>
-      </c>
-      <c r="I123" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J123" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="124" spans="2:10" ht="15" customHeight="1">
-      <c r="B124" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C124" s="13"/>
-      <c r="D124" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F124" s="14">
-        <v>-27000</v>
-      </c>
-      <c r="G124" s="15">
-        <v>-139.29</v>
-      </c>
-      <c r="H124" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="I124" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J124" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="128" spans="2:9" ht="15" customHeight="1">
-      <c r="B128" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="C128" s="22"/>
-      <c r="D128" s="22"/>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22"/>
-      <c r="G128" s="22"/>
-      <c r="H128" s="22"/>
-      <c r="I128" s="22"/>
-    </row>
-    <row r="132" spans="2:9" ht="15" customHeight="1">
-      <c r="B132" s="13" t="s">
-        <v>222</v>
       </c>
       <c r="C132" s="22"/>
       <c r="D132" s="22"/>
@@ -4652,11 +4583,10 @@
       <c r="F132" s="22"/>
       <c r="G132" s="22"/>
       <c r="H132" s="22"/>
-      <c r="I132" s="22"/>
-    </row>
-    <row r="133" spans="2:8" ht="15" customHeight="1">
-      <c r="B133" s="13" t="s">
-        <v>223</v>
+    </row>
+    <row r="133" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B133" s="23" t="s">
+        <v>220</v>
       </c>
       <c r="C133" s="22"/>
       <c r="D133" s="22"/>
@@ -4665,9 +4595,9 @@
       <c r="G133" s="22"/>
       <c r="H133" s="22"/>
     </row>
-    <row r="134" spans="2:8" ht="15" customHeight="1">
-      <c r="B134" s="13" t="s">
-        <v>224</v>
+    <row r="134" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B134" s="23" t="s">
+        <v>221</v>
       </c>
       <c r="C134" s="22"/>
       <c r="D134" s="22"/>
@@ -4676,9 +4606,9 @@
       <c r="G134" s="22"/>
       <c r="H134" s="22"/>
     </row>
-    <row r="135" spans="2:8" ht="15" customHeight="1">
-      <c r="B135" s="13" t="s">
-        <v>225</v>
+    <row r="135" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B135" s="23" t="s">
+        <v>222</v>
       </c>
       <c r="C135" s="22"/>
       <c r="D135" s="22"/>
@@ -4687,67 +4617,34 @@
       <c r="G135" s="22"/>
       <c r="H135" s="22"/>
     </row>
-    <row r="136" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B136" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="C136" s="22"/>
-      <c r="D136" s="22"/>
-      <c r="E136" s="22"/>
-      <c r="F136" s="22"/>
-      <c r="G136" s="22"/>
-      <c r="H136" s="22"/>
-    </row>
-    <row r="137" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B137" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="C137" s="22"/>
-      <c r="D137" s="22"/>
-      <c r="E137" s="22"/>
-      <c r="F137" s="22"/>
-      <c r="G137" s="22"/>
-      <c r="H137" s="22"/>
-    </row>
-    <row r="138" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B138" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="C138" s="22"/>
-      <c r="D138" s="22"/>
-      <c r="E138" s="22"/>
-      <c r="F138" s="22"/>
-      <c r="G138" s="22"/>
-      <c r="H138" s="22"/>
-    </row>
-    <row r="141" ht="15">
-      <c r="B141" s="22" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="156" ht="15">
-      <c r="B156" s="22" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="157" ht="15">
-      <c r="B157" s="22" t="s">
-        <v>231</v>
+    <row r="138" ht="15">
+      <c r="B138" s="22" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="153" ht="15">
+      <c r="B153" s="22" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="154" ht="15">
+      <c r="B154" s="22" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B138:H138"/>
+    <mergeCell ref="B135:H135"/>
+    <mergeCell ref="B130:H130"/>
+    <mergeCell ref="B131:H131"/>
+    <mergeCell ref="B132:H132"/>
     <mergeCell ref="B133:H133"/>
     <mergeCell ref="B134:H134"/>
-    <mergeCell ref="B135:H135"/>
-    <mergeCell ref="B136:H136"/>
-    <mergeCell ref="B137:H137"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B128:I128"/>
-    <mergeCell ref="B132:I132"/>
+    <mergeCell ref="B125:I125"/>
+    <mergeCell ref="B129:I129"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
